--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-04).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-04).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-181</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>R$ 1.730.474,69</t>
-  </si>
-  <si>
-    <t>R$ 9.012,89
-R$ 9.173,93</t>
-  </si>
-  <si>
-    <t>(3.4%)
-(1.7%)</t>
-  </si>
-  <si>
-    <t>96.4</t>
-  </si>
-  <si>
-    <t>(6.6%)</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>(38.6%)</t>
+185</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>R$ 1.763.293,63</t>
+  </si>
+  <si>
+    <t>R$ 8.996,40
+R$ 9.152,97</t>
+  </si>
+  <si>
+    <t>(3.6%)
+(1.9%)</t>
+  </si>
+  <si>
+    <t>96.3</t>
+  </si>
+  <si>
+    <t>(6.4%)</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>(38.2%)</t>
   </si>
   <si>
     <t>2.9%</t>
@@ -947,34 +947,34 @@
     <t>0.7%</t>
   </si>
   <si>
-    <t>29.7</t>
-  </si>
-  <si>
-    <t>59.2%</t>
-  </si>
-  <si>
-    <t>16.2%</t>
+    <t>30.0</t>
+  </si>
+  <si>
+    <t>59.5%</t>
+  </si>
+  <si>
+    <t>16.9%</t>
   </si>
   <si>
     <t>6.5</t>
   </si>
   <si>
-    <t>7.8</t>
-  </si>
-  <si>
-    <t>14.6</t>
-  </si>
-  <si>
-    <t>21.2</t>
-  </si>
-  <si>
-    <t>60.9%</t>
-  </si>
-  <si>
-    <t>-R$ 56.548,17</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>14.7</t>
+  </si>
+  <si>
+    <t>21.4</t>
+  </si>
+  <si>
+    <t>60.4%</t>
+  </si>
+  <si>
+    <t>-R$ 56.947,77</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -4424,7 +4424,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4460,25 +4460,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>11943.08</v>
+      </c>
+      <c r="P24" s="5">
+        <v>11943.08</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>-0.057755575086350097</v>
+      </c>
+      <c r="R24" s="7">
+        <v>133</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.05673758865248224</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0.32360087180191371</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.01740747780304578</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.019328221865716384</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.0037443021398165296</v>
+      </c>
+      <c r="X24" s="8">
+        <v>39.311052631578953</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.62105263157894741</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.5368421052631579</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>12.736153846153847</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>8.6907021052631581</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>29.991754736842104</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.24210526315789474</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-399.60000000000002</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5960,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5996,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>7837.46</v>
+      </c>
+      <c r="P36" s="5">
+        <v>7837.46</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.047217560475035114</v>
+      </c>
+      <c r="R36" s="7">
+        <v>130</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.68831168831168821</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.37577540427638545</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.0029646467095206862</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.049327014109162917</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.015114399307939052</v>
+      </c>
+      <c r="X36" s="8">
+        <v>38.776211818181821</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.94545454545454544</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.41818181818181815</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.0628787878787875</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>19.342834579439252</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>24.270204</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>30.556515454545455</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.49090909090909091</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7881,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7917,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1200.3399999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1200.3399999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.2888588240347032</v>
+      </c>
+      <c r="R51" s="7">
+        <v>13</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0.18181818181818188</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.3721195661229319</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.029674092340503527</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.087925920989053108</v>
+      </c>
+      <c r="X51" s="8">
+        <v>33.186660000000003</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.0051307692307692</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>16.449999999999999</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>20.913333000000002</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>27.836660000000002</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12636,7 +12742,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12675,7 +12781,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12709,25 +12815,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>11838.059999999999</v>
+      </c>
+      <c r="P89" s="5">
+        <v>11838.059999999999</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.25754493091025865</v>
+      </c>
+      <c r="R89" s="7">
+        <v>106</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.30263157894736847</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-0.084242587045512532</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.39276949094699642</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.01658797978722865</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0048884276646680288</v>
+      </c>
+      <c r="X89" s="8">
+        <v>47.944551923076922</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.62264150943396224</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>10.432857142857143</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>20.029251020408164</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>34.757843137254902</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.17307692307692307</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16751,7 +16891,7 @@
         <v>-116.90000000000001</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17013,7 +17153,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17406,7 +17546,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18583,7 +18723,7 @@
         <v>-103.5</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18714,7 +18854,7 @@
         <v>-140</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20901,7 +21041,7 @@
         <v>-5099.6199999999999</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21028,7 +21168,7 @@
         <v>-160.19999999999999</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22185,7 +22325,7 @@
         <v>-2035.26</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24263,7 +24403,9 @@
       <c r="AB179" s="8">
         <v>1.8987179487179486</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>4.5695499999999996</v>
+      </c>
       <c r="AD179" s="8">
         <v>11.473930769230769</v>
       </c>
@@ -28348,7 +28490,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
